--- a/files/tablitsa-rashodov.xlsx
+++ b/files/tablitsa-rashodov.xlsx
@@ -8,7 +8,9 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Расходы на ребёнка" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="1. Фактические расходы" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="2. Планируемые расходы" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="3. Итоговая сводка" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,12 +22,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="43">
-  <si>
-    <t xml:space="preserve">ТАБЛИЦА РАСХОДОВ НА СОДЕРЖАНИЕ РЕБЁНКА</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Для приложения к исковому заявлению о взыскании алиментов в твёрдой денежной сумме</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="94">
+  <si>
+    <t xml:space="preserve">ТАБЛИЦА РАСХОДОВ НА РЕБЁНКА ДЛЯ СУДА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблица 1. Фактические (понесённые) расходы с подтверждающими документами</t>
   </si>
   <si>
     <t xml:space="preserve">ФИО ребёнка:</t>
@@ -34,7 +36,7 @@
     <t xml:space="preserve">Дата рождения:</t>
   </si>
   <si>
-    <t xml:space="preserve">Период расчёта (месяц/год):</t>
+    <t xml:space="preserve">Период учёта расходов (например: январь–июнь 2026):</t>
   </si>
   <si>
     <t xml:space="preserve">№</t>
@@ -43,123 +45,280 @@
     <t xml:space="preserve">Категория расходов</t>
   </si>
   <si>
-    <t xml:space="preserve">Сумма в месяц, руб.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Подтверждающий документ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Питание</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чеки из магазинов</t>
+    <t xml:space="preserve">Сумма (руб.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтверждающие документы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Примечания / пояснения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Питание (продукты, питание в школе/саду)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чеки, квитанции об оплате питания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разделить домашнее и организованное питание</t>
   </si>
   <si>
     <t xml:space="preserve">Одежда и обувь</t>
   </si>
   <si>
+    <t xml:space="preserve">Чеки, товарные чеки, выписки с карт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Укажите сезонность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гигиена и уход</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чеки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Для младенцев — подгузники отдельно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Медицина (лекарства, анализы, врачи)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рецепты, назначения, чеки, договоры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Приложите назначения врача</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Образование (школа, сад, кружки, репетиторы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Договоры, квитанции, чеки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Укажите названия секций/кружков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Канцелярские товары и принадлежности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Особенно актуально перед 1 сентября</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Транспорт (проездной, такси, бензин)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Билеты, чеки, выписки с транспортных карт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Маршрут, если ребёнок ездит сам</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Развлечения и досуг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Билеты, чеки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупные покупки (техника, велосипед и т.д.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чеки, договоры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разбейте на месяцы: сумма ÷ кол-во месяцев использования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прочие расходы (стрижки, фото, страховка)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Чеки, квитанции</t>
   </si>
   <si>
-    <t xml:space="preserve">Детский сад / школа</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Договор, квитанции об оплате</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Кружки и секции</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Договор, квитанции</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Репетиторы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Лекарства и медицинские расходы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Рецепты, чеки, квитанции</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Стоматология</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Квитанции</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Средства гигиены</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чеки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Игрушки и развивающие материалы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Досуг и культурные мероприятия</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Чеки, билеты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Транспортные расходы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Билеты, чеки</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Интернет / телефон (доля на ребёнка)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Иные расходы</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ИТОГО В МЕСЯЦ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СПРАВОЧНО</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Прожиточный минимум на ребёнка в регионе, руб.:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Доля обязанности каждого родителя:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Запрашиваемая сумма алиментов в месяц, руб.:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">КАК ЗАПОЛНЯТЬ:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Укажите среднемесячные расходы за последние 3–6 месяцев.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. К иску приложите все подтверждающие документы (чеки, квитанции, договоры).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Если документов нет — укажите примерную сумму и опишите расходы в тексте иска.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Итоговая сумма делится на 2: содержание ребёнка — обязанность обоих родителей в равных долях.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">«По рекомендации» — юридические документы онлайн  ·  rekoyur.ru  ·  t.me/a_likhacheva2026  ·  @rek.yur  ·  +7 992 001-19-95</t>
+    <t xml:space="preserve">Опишите кратко</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИТОГО фактических расходов за период</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Среднемесячные расходы (÷ кол-во месяцев периода)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← Введите итог ÷ количество месяцев</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАК ЗАПОЛНЯТЬ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Приложите к таблице копии всех чеков, квитанций, договоров — сгруппированные по категориям.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Если расходы кажутся высокими — укажите рыночные цены (прайс клиники, спортшколы и т.д.).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. В «Примечаниях» поясняйте, почему трата необходима (например: «по назначению врача»).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Крупные покупки разбейте на месяцы: куртка 10 000 руб. на 2 года = 417 руб./мес.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Суммы должны быть разумными и соответствовать уровню жизни в вашем регионе.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«По рекомендации» — rekoyur.ru  ·  t.me/a_likhacheva2026  ·  @rek.yur  ·  +7 992 001-19-95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Таблица 2. Планируемые (будущие) расходы и нужды ребёнка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Категория нужд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сумма (руб./мес.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Срок / периодичность</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обоснование и подтверждение</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Регулярные расходы (питание, гигиена, транспорт)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ежемесячно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Базовые потребности — опирайтесь на прошлые траты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сезонная одежда и обувь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1–2 раза в год</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост ребёнка, износ вещей. Приложите список необходимых вещей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дополнительное образование (кружки, секции, курсы)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По графику занятий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Развитие ребёнка. Договор или прайс организации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Медицинские нужды (лечение, профилактика, витамины)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По назначению врача</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Состояние здоровья. Выписка из медкарты, назначение врача</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Учебные материалы (учебники, пособия, гаджеты)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Перед учебным годом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требования школы. Списки от школы, прайсы магазинов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Отдых и реабилитация (лагерь, санаторий, море)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На каникулах</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оздоровление. Брошюры лагерей, договоры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупные приобретения (мебель, инвентарь, техника)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Однократно / редко</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Потребности ребёнка. Прайс-листы, описание необходимости</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИТОГО планируемых расходов в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИТОГОВАЯ ФОРМУЛИРОВКА ДЛЯ ИСКОВОГО ЗАЯВЛЕНИЯ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На содержание несовершеннолетнего ребёнка ежемесячно требуется сумма в размере _______ руб., из которых:
+• фактически понесённые расходы за последние ___ месяцев составили _______ руб.;
+• планируемые расходы, подтверждённые документами, — _______ руб./мес.
+Прошу взыскать алименты в твёрдой денежной сумме в размере _______ руб. ежемесячно.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВАЖНЫЕ РЕКОМЕНДАЦИИ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Суммы должны быть разумными и соответствовать уровню жизни в вашем регионе.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Пишите чётко и без эмоций: «по назначению врача», «согласно договору №…», «по учебной программе».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Избегайте завышения без доказательств — это снижает доверие суда ко всей таблице.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Соедините Таблицу 1 и Таблицу 2 в одном документе при подаче иска.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИТОГОВАЯ СВОДКА</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заполните данные о ребёнке и вставьте итоги из Листов 1 и 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ФИО ребёнка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прожиточный минимум на ребёнка в регионе (руб./мес.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Среднемесячные фактические расходы (из Листа 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Планируемые расходы в месяц (из Листа 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИТОГО расходов в месяц</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Доля истца (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЗАПРАШИВАЕМАЯ СУММА АЛИМЕНТОВ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сумма к взысканию в месяц (укажите вручную):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кратно прожиточному минимуму:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">⚖️ Окончательный размер алиментов определяет суд. Укажите обоснованную сумму и приложите документы.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot; ПМ&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,7 +343,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
+      <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -192,8 +351,8 @@
     </font>
     <font>
       <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF6B7A75"/>
+      <sz val="9"/>
+      <color rgb="FF667085"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -201,14 +360,7 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF1B2B27"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1B2B27"/>
+      <color rgb="FF152033"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -222,9 +374,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <sz val="10"/>
+      <color rgb="FF152033"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <color rgb="FF6B7A75"/>
+      <color rgb="FF152033"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -247,15 +405,15 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF1F5C52"/>
+      <sz val="11"/>
+      <color rgb="FF0F1A2B"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
-      <color rgb="FF6B7A75"/>
+      <color rgb="FF667085"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -265,6 +423,29 @@
       <i val="true"/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF152033"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF0F1A2B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF667085"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -279,8 +460,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F5C52"/>
-        <bgColor rgb="FF008080"/>
+        <fgColor rgb="FF0F1A2B"/>
+        <bgColor rgb="FF152033"/>
       </patternFill>
     </fill>
     <fill>
@@ -309,18 +490,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9E9E2"/>
+        <fgColor rgb="FFEDE0C4"/>
         <bgColor rgb="FFF1EFEA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1B2B27"/>
-        <bgColor rgb="FF333300"/>
+        <fgColor rgb="FF1F5C52"/>
+        <bgColor rgb="FF008080"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -333,7 +514,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color rgb="FF1F5C52"/>
+        <color rgb="FFC9A24B"/>
       </bottom>
       <diagonal/>
     </border>
@@ -354,6 +535,21 @@
     </border>
     <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
+        <color rgb="FFC9A24B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC9A24B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFC9A24B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFC9A24B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
         <color rgb="FFC9DDD6"/>
       </left>
       <right/>
@@ -362,6 +558,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFC9DDD6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="medium">
+        <color rgb="FFC9A24B"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC9A24B"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC9A24B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC9A24B"/>
       </bottom>
       <diagonal/>
     </border>
@@ -391,7 +602,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="37">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -408,43 +619,47 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -456,28 +671,84 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -506,7 +777,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF1F5C52"/>
       <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF6B7A75"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFBF6EC"/>
@@ -526,27 +797,27 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFF1EFEA"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFF9E9E2"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFEDE0C4"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF667085"/>
+      <rgbColor rgb="FFC9A24B"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF0F1A2B"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF1B2B27"/>
+      <rgbColor rgb="FF152033"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -732,30 +1003,32 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -765,6 +1038,7 @@
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
@@ -773,6 +1047,7 @@
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
@@ -781,9 +1056,10 @@
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
         <v>5</v>
       </c>
@@ -796,281 +1072,658 @@
       <c r="D8" s="5" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>11</v>
+      <c r="B10" s="12" t="s">
+        <v>13</v>
       </c>
       <c r="C10" s="8"/>
-      <c r="D10" s="12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D10" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>15</v>
+      <c r="B12" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="C12" s="8"/>
-      <c r="D12" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B14" s="11" t="s">
-        <v>18</v>
+      <c r="B14" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="C14" s="8"/>
-      <c r="D14" s="12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D14" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>22</v>
+      <c r="B16" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="C16" s="8"/>
-      <c r="D16" s="12" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="D16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>25</v>
+      <c r="B18" s="12" t="s">
+        <v>35</v>
       </c>
       <c r="C18" s="8"/>
-      <c r="D18" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="8"/>
-      <c r="D19" s="9" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
+      <c r="D18" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="14"/>
+      <c r="C19" s="15" t="n">
+        <f aca="false">SUM(C9:C18)</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-    </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="14" t="n">
-        <f aca="false">SUM(C9:C21)</f>
+      <c r="A21" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" s="17"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="21"/>
+      <c r="D24" s="21"/>
+      <c r="E24" s="21"/>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A30:E30"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="15"/>
-    </row>
-    <row r="23" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="16" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-    </row>
-    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D26" s="18"/>
-    </row>
-    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-    </row>
-    <row r="28" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-    </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="20"/>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20"/>
-    </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="20"/>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20"/>
-    </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-    </row>
-    <row r="34" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="35" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="8"/>
+      <c r="D6" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="8"/>
+      <c r="D7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="8"/>
+      <c r="D10" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15" t="n">
+        <f aca="false">SUM(C5:C11)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+    </row>
+    <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+    </row>
+    <row r="16" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+    </row>
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A35:D35"/>
+  <mergeCells count="11">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="A23:E23"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="26"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B5" s="26"/>
+    </row>
+    <row r="6" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="28"/>
+    </row>
+    <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="28"/>
+    </row>
+    <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="30" t="n">
+        <f aca="false">B7+B8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="30" t="n">
+        <f aca="false">B9/2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="31" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="31"/>
+    </row>
+    <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="33"/>
+    </row>
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" s="35" t="str">
+        <f aca="false">IF(B4&gt;0,B13/B4,"введите ПМ")</f>
+        <v>введите ПМ</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="36"/>
+    </row>
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
